--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="13125" windowHeight="4995"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -16,9 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
-    <t>退款单号</t>
-  </si>
-  <si>
     <t>订单号</t>
   </si>
   <si>
@@ -37,6 +34,9 @@
     <t>汇率</t>
   </si>
   <si>
+    <t>结算汇率</t>
+  </si>
+  <si>
     <t>下单人</t>
   </si>
   <si>
@@ -73,9 +73,6 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.refundId}</t>
-  </si>
-  <si>
     <t>{.platformOrderId}</t>
   </si>
   <si>
@@ -92,6 +89,9 @@
   </si>
   <si>
     <t>{.currencyRate}</t>
+  </si>
+  <si>
+    <t>{.cnySettleRate}</t>
   </si>
   <si>
     <t>{.buyerName}</t>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13125" windowHeight="4995"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,21 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
-  <si>
-    <t>订单号</t>
-  </si>
-  <si>
-    <t>平台名称</t>
-  </si>
-  <si>
-    <t>站点</t>
-  </si>
-  <si>
-    <t>店铺名称</t>
-  </si>
-  <si>
-    <t>订单销售额[原币种]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+  <si>
+    <t>*订单号</t>
+  </si>
+  <si>
+    <t>*平台名称</t>
+  </si>
+  <si>
+    <t>*站点</t>
+  </si>
+  <si>
+    <t>*店铺名称</t>
+  </si>
+  <si>
+    <t>*订单销售额[原币种]</t>
   </si>
   <si>
     <t>汇率</t>
@@ -37,7 +37,7 @@
     <t>结算汇率</t>
   </si>
   <si>
-    <t>下单人</t>
+    <t>*下单人</t>
   </si>
   <si>
     <t>下单电话1</t>
@@ -52,10 +52,10 @@
     <t>下单地址2</t>
   </si>
   <si>
-    <t>国家名称</t>
-  </si>
-  <si>
-    <t>订单状态</t>
+    <t>*国家名称</t>
+  </si>
+  <si>
+    <t>*订单状态</t>
   </si>
   <si>
     <t>订单下单时间</t>
@@ -64,12 +64,24 @@
     <t>订单发货时间</t>
   </si>
   <si>
-    <t>销售员</t>
+    <t>*销售员</t>
   </si>
   <si>
     <t>币种</t>
   </si>
   <si>
+    <t>*SKU</t>
+  </si>
+  <si>
+    <t>*品名</t>
+  </si>
+  <si>
+    <t>*单价</t>
+  </si>
+  <si>
+    <t>*数量</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -122,6 +134,18 @@
   </si>
   <si>
     <t>{.currencyCode}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.itemName}</t>
+  </si>
+  <si>
+    <t>{.sellPrice}</t>
+  </si>
+  <si>
+    <t>{.quantity}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -769,11 +793,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1095,10 +1122,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:19">
+    <row r="1" customFormat="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1156,67 +1183,101 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="T2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576 F3:F1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -793,11 +793,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1254,16 +1257,16 @@
       <c r="S2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="3" t="s">
         <v>44</v>
       </c>
     </row>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -58,7 +58,7 @@
     <t>*订单状态</t>
   </si>
   <si>
-    <t>订单下单时间</t>
+    <t>*订单下单时间</t>
   </si>
   <si>
     <t>订单发货时间</t>
@@ -793,14 +793,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1257,21 +1254,21 @@
       <c r="S2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="2" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="6">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
@@ -1280,6 +1277,21 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:G2">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+      <formula1>"配货中,已发货,已完成,已作废"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -1268,7 +1268,14 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+      <formula1>"配货中,已发货,已完成,已作废"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:G2">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
@@ -1277,20 +1284,17 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:G2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
       <formula1>0</formula1>
-      <formula2>9999999999999990000</formula2>
+      <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
-      <formula1>"配货中,已发货,已完成,已作废"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>0</formula1>
-      <formula2>99999999999999900000</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
+      <formula2>9.99999999999999E+24</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>*订单号</t>
   </si>
@@ -67,6 +67,9 @@
     <t>*销售员</t>
   </si>
   <si>
+    <t>*销售事业部</t>
+  </si>
+  <si>
     <t>币种</t>
   </si>
   <si>
@@ -88,7 +91,7 @@
     <t>{.platformOrderId}</t>
   </si>
   <si>
-    <t>{.platformName}</t>
+    <t>{.sourcePlatform}</t>
   </si>
   <si>
     <t>{.site}</t>
@@ -121,7 +124,10 @@
     <t>{.secondStreet}</t>
   </si>
   <si>
-    <t>{.orderState}</t>
+    <t>{.countryNameCn}</t>
+  </si>
+  <si>
+    <t>{.orderStateName}</t>
   </si>
   <si>
     <t>{.platformCreateTime}</t>
@@ -131,6 +137,9 @@
   </si>
   <si>
     <t>{.chargeName}</t>
+  </si>
+  <si>
+    <t>{.deptName}</t>
   </si>
   <si>
     <t>{.currencyCode}</t>
@@ -1122,10 +1131,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:23">
+    <row r="1" customFormat="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1183,7 +1192,7 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
@@ -1195,86 +1204,96 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
-      <formula1>"配货中,已发货,已完成,已作废"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:G2">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 N3:N1048576">
+      <formula1>"配货中,已发货,已完成,已作废"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+24</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
       <formula1>0</formula1>
@@ -1288,13 +1307,9 @@
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+24</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -1288,9 +1288,6 @@
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 N3:N1048576">
-      <formula1>"配货中,已发货,已完成,已作废"</formula1>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+24</formula2>
@@ -1302,6 +1299,9 @@
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576 F3:F1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+      <formula1>"配货中,已发货,已完成,已作废,退货,退款"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
       <formula1>25569</formula1>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfo.xlsx
@@ -130,10 +130,10 @@
     <t>{.orderStateName}</t>
   </si>
   <si>
-    <t>{.platformCreateTime}</t>
-  </si>
-  <si>
-    <t>{.deliveryTime}</t>
+    <t>{.platformCreateTimeStr}</t>
+  </si>
+  <si>
+    <t>{.deliveryTimeStr}</t>
   </si>
   <si>
     <t>{.chargeName}</t>
@@ -1303,7 +1303,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>"配货中,已发货,已完成,已作废,退货,退款"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O1048576 P3:P1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
